--- a/pacjenci/MATEUSZ KRÓL.xlsx
+++ b/pacjenci/MATEUSZ KRÓL.xlsx
@@ -413,147 +413,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>29.09.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina postać nieklasyczna (NLPHL) na podstawie hist-pat w. chłonnego szyjnego po stronie lewej. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 104%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywne metabolicznie węzły chłonne:  - grupy 2 po stronie lewej, wielkości 13x12x20mm, SUV max 4,3; - grupy 3 po stronie lewej, wielkości 19x14x17mm, SUV max 5,2. Asymetrycznie wzmożony metabolizm FDG w prawym fałdzie nalewkowo-nagłośniowym, SUV max 5,9 - do kontroli laryngologicznej [Im fuz 81]. Niejednorodny metabolizm FDG w tarczycy - do ew. kontroli w USG.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej. Dość liczne drobne węzły chłonne podżuchwowe, więcej i większe po stronie lewej, wielkości do 12mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe prawe wielkości do 22x13mm. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w topografii żołądka oraz pętli jelitowych SUV max do 4,4 - do kontroli w kolonoskopii. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dodatkowa śledziona  wielkości ok. 9x7mm. Wodniak lewego jądra - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiana osteolityczno-sklerotyczna w przymostkowym odcinku prawego obojczyka. Spłycenie fizjologicznych krzywizn kregosłupa. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych szyjnych po stronie lewej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>5.9</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>30.03.2023</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina postać nieklasyczna (NLPHL) na podstawie hist-pat w. chłonnego szyjnego po stronie lewej. Ocena remisji choroby 3 miesiące po zakończeniu IFRT.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 85%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Pobudzenie metaboliczne na tylnej ścianie nosogardła, SUV max 5,0- do ew. kontroli laryngologicznej.  Asymetryczne pobudzenie metaboliczne w śliniance podżuchwowej prawej, SUV max 3,7- do ew. kontroli laryngologicznej.  Asymetrycznie wzmożony metabolizm FDG w prawym fałdzie nalewkowo-nagłośniowym- opisywane już poprzednio [Im fuz 80]. Niejednorodny metabolizm FDG w tarczycy.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w segm. 5 obu płuc. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Pobudzenie metaboliczne w części wpustowej żołądka- czynnościowo? Odcinkowo wzmożony metabolizm FDG w topografii pętli jelitowych -czynnościowo. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dodatkowa śledziona  wielkości ok. 9x7mm. Drobne zwapnienia w topografii najądrzy. Wodniak lewego jądra - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiana osteolityczno-sklerotyczna w przymostkowym odcinku prawego obojczyka. Spłycenie fizjologicznych krzywizn kregosłupa. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax 2,5. Prawy płat wątroby SUVmax do 3,7.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnych metabolicznie węzłów chłonnych. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/MATEUSZ KRÓL.xlsx
+++ b/pacjenci/MATEUSZ KRÓL.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 104%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne:  - grupy 2 po stronie lewej, wielkości 13x12x20mm, SUV max 4,3; - grupy 3 po stronie lewej, wielkości 19x14x17mm, SUV max 5,2. Asymetrycznie wzmożony metabolizm FDG w prawym fałdzie nalewkowo-nagłośniowym, SUV max 5,9 - do kontroli laryngologicznej [Im fuz 81]. Niejednorodny metabolizm FDG w tarczycy - do ew. kontroli w USG.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej. Dość liczne drobne węzły chłonne podżuchwowe, więcej i większe po stronie lewej, wielkości do 12mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe prawe wielkości do 22x13mm. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w topografii żołądka oraz pętli jelitowych SUV max do 4,4 - do kontroli w kolonoskopii. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dodatkowa śledziona  wielkości ok. 9x7mm. Wodniak lewego jądra - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiana osteolityczno-sklerotyczna w przymostkowym odcinku prawego obojczyka. Spłycenie fizjologicznych krzywizn kregosłupa. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 3,5.</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne:  - grupy 2 po stronie lewej, wielkości 13x12x20mm, SUV max 4,3; - grupy 3 po stronie lewej, wielkości 19x14x17mm, SUV max 5,2. Asymetrycznie wzmożony metabolizm FDG w prawym fałdzie nalewkowo-nagłośniowym, SUV max 5,9 - do kontroli laryngologicznej [Im fuz 81]. Niejednorodny metabolizm FDG w tarczycy - do ew. kontroli w USG.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej. Dość liczne drobne węzły chłonne podżuchwowe, więcej i większe po stronie lewej, wielkości do 12mm.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe prawe wielkości do 22x13mm. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Odcinkowo wzmożony metabolizm FDG w topografii żołądka oraz pętli jelitowych SUV max do 4,4 - do kontroli w kolonoskopii. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dodatkowa śledziona  wielkości ok. 9x7mm. Wodniak lewego jądra - do kontroli urologicznej.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiana osteolityczno-sklerotyczna w przymostkowym odcinku prawego obojczyka. Spłycenie fizjologicznych krzywizn kregosłupa. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych szyjnych po stronie lewej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>5.9</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 85%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Pobudzenie metaboliczne na tylnej ścianie nosogardła, SUV max 5,0- do ew. kontroli laryngologicznej.  Asymetryczne pobudzenie metaboliczne w śliniance podżuchwowej prawej, SUV max 3,7- do ew. kontroli laryngologicznej.  Asymetrycznie wzmożony metabolizm FDG w prawym fałdzie nalewkowo-nagłośniowym- opisywane już poprzednio [Im fuz 80]. Niejednorodny metabolizm FDG w tarczycy.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w segm. 5 obu płuc. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Pobudzenie metaboliczne w części wpustowej żołądka- czynnościowo? Odcinkowo wzmożony metabolizm FDG w topografii pętli jelitowych -czynnościowo. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dodatkowa śledziona  wielkości ok. 9x7mm. Drobne zwapnienia w topografii najądrzy. Wodniak lewego jądra - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiana osteolityczno-sklerotyczna w przymostkowym odcinku prawego obojczyka. Spłycenie fizjologicznych krzywizn kregosłupa. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax 2,5. Prawy płat wątroby SUVmax do 3,7.</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne na tylnej ścianie nosogardła, SUV max 5,0- do ew. kontroli laryngologicznej.  Asymetryczne pobudzenie metaboliczne w śliniance podżuchwowej prawej, SUV max 3,7- do ew. kontroli laryngologicznej.  Asymetrycznie wzmożony metabolizm FDG w prawym fałdzie nalewkowo-nagłośniowym- opisywane już poprzednio [Im fuz 80]. Niejednorodny metabolizm FDG w tarczycy.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w segm. 5 obu płuc. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w części wpustowej żołądka- czynnościowo? Odcinkowo wzmożony metabolizm FDG w topografii pętli jelitowych -czynnościowo. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dodatkowa śledziona  wielkości ok. 9x7mm. Drobne zwapnienia w topografii najądrzy. Wodniak lewego jądra - do kontroli urologicznej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiana osteolityczno-sklerotyczna w przymostkowym odcinku prawego obojczyka. Spłycenie fizjologicznych krzywizn kregosłupa. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnych metabolicznie węzłów chłonnych. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>5</v>
       </c>
     </row>
